--- a/aReport_card/2025_2026/Second_term/JSS3/Second_term_JSS3_Home_Economics.xlsx
+++ b/aReport_card/2025_2026/Second_term/JSS3/Second_term_JSS3_Home_Economics.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81293619-9CB7-405B-880E-A29AE43534D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F41470E-B8B9-42A3-BCF4-E9DF50B8C09B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -87,8 +87,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -116,8 +124,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -465,23 +474,23 @@
     <col min="3" max="6" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -493,17 +502,17 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E2">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F2">
         <f t="shared" ref="F2:F9" si="0">SUM(C2:E2)</f>
-        <v>74</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -514,17 +523,17 @@
         <v>9</v>
       </c>
       <c r="C3">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E3">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F3">
         <f t="shared" si="0"/>
-        <v>51</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -535,17 +544,17 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E4">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F4">
         <f t="shared" si="0"/>
-        <v>81</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -556,17 +565,17 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>25</v>
+        <v>34.5</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E5">
-        <v>26</v>
+        <v>26.5</v>
       </c>
       <c r="F5">
         <f t="shared" si="0"/>
-        <v>51</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -577,17 +586,17 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D6">
         <v>14</v>
       </c>
       <c r="E6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F6">
         <f t="shared" si="0"/>
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -598,17 +607,17 @@
         <v>17</v>
       </c>
       <c r="C7">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F7">
         <f t="shared" si="0"/>
-        <v>65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -619,17 +628,17 @@
         <v>19</v>
       </c>
       <c r="C8">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D8">
         <v>14</v>
       </c>
       <c r="E8">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F8">
         <f t="shared" si="0"/>
-        <v>65</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -640,17 +649,17 @@
         <v>21</v>
       </c>
       <c r="C9">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D9">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="E9">
-        <v>26</v>
+        <v>27.5</v>
       </c>
       <c r="F9">
         <f t="shared" si="0"/>
-        <v>65</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
